--- a/fhir/finnish-smart/StructureDefinition-fi-smart-medication.xlsx
+++ b/fhir/finnish-smart/StructureDefinition-fi-smart-medication.xlsx
@@ -9,14 +9,11 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$29</definedName>
-  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="253">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-rc2</t>
+    <t>2.0.0-rc3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-11T17:07:13+03:00</t>
+    <t>2025-06-01T15:36:45+03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ipa/StructureDefinition/ipa-medication</t>
+    <t>https://hl7.fi/fhir/finnish-base-profiles/StructureDefinition/fi-base-medication</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -561,7 +558,7 @@
     <t>Medication.manufacturer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(https://hl7.fi/fhir/finnish-base-profiles/StructureDefinition/fi-base-organization)
 </t>
   </si>
   <si>
@@ -708,10 +705,27 @@
     <t>The ingredient may reference a substance (for example, amoxicillin) or another medication (for example in the case of a compounded product, Glaxal Base).</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>.player</t>
   </si>
   <si>
     <t>RXC-2-Component Code  if medication: RXO-1-Requested Give Code / RXE-2-Give Code / RXD-2-Dispense/Give Code / RXG-4-Give Code / RXA-5-Administered Code</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemReference</t>
+  </si>
+  <si>
+    <t>itemReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Substance|https://hl7.fi/fhir/finnish-base-profiles/StructureDefinition/fi-base-medication|https://hl7.fi/fhir/finnish-base-profiles/StructureDefinition/fi-base-patient-medication)
+</t>
   </si>
   <si>
     <t>Medication.ingredient.isActive</t>
@@ -927,21 +941,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -1115,12 +1114,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN29"/>
+  <dimension ref="A1:AN30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="32.10546875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="34.99609375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="32.10546875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="9.79296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="11.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
@@ -1128,7 +1127,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="26.21875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="148.640625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1281,7 +1280,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -1393,7 +1392,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>86</v>
       </c>
@@ -1507,7 +1506,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>94</v>
       </c>
@@ -1619,7 +1618,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>100</v>
       </c>
@@ -1733,7 +1732,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>106</v>
       </c>
@@ -1847,7 +1846,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>115</v>
       </c>
@@ -1961,7 +1960,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>123</v>
       </c>
@@ -2075,7 +2074,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>131</v>
       </c>
@@ -2189,7 +2188,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>139</v>
       </c>
@@ -2305,7 +2304,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>144</v>
       </c>
@@ -2419,7 +2418,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>151</v>
       </c>
@@ -2432,13 +2431,13 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>77</v>
@@ -2533,7 +2532,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>163</v>
       </c>
@@ -2647,7 +2646,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>171</v>
       </c>
@@ -2759,7 +2758,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>179</v>
       </c>
@@ -2873,7 +2872,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>188</v>
       </c>
@@ -2985,7 +2984,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>193</v>
       </c>
@@ -3099,7 +3098,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>199</v>
       </c>
@@ -3211,7 +3210,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>205</v>
       </c>
@@ -3325,7 +3324,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>208</v>
       </c>
@@ -3441,7 +3440,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>213</v>
       </c>
@@ -3516,16 +3515,14 @@
         <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>77</v>
+        <v>219</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>213</v>
@@ -3546,23 +3543,25 @@
         <v>159</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="22" hidden="true">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>77</v>
       </c>
@@ -3583,17 +3582,17 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -3642,10 +3641,10 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>87</v>
@@ -3657,24 +3656,24 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>77</v>
+        <v>159</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AM22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" hidden="true">
-      <c r="A23" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="B23" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3697,7 +3696,7 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>189</v>
+        <v>226</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>227</v>
@@ -3706,7 +3705,9 @@
         <v>228</v>
       </c>
       <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
       </c>
@@ -3754,7 +3755,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3769,19 +3770,19 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>229</v>
+        <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="24" hidden="true">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>231</v>
       </c>
@@ -3809,7 +3810,7 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>232</v>
@@ -3881,24 +3882,24 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>175</v>
+        <v>234</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>234</v>
+        <v>192</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="25" hidden="true">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3921,13 +3922,13 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3978,7 +3979,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>203</v>
+        <v>236</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -3990,13 +3991,13 @@
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4005,23 +4006,23 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4033,17 +4034,15 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>133</v>
+        <v>200</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>134</v>
+        <v>201</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4092,19 +4091,19 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
@@ -4119,16 +4118,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>209</v>
+        <v>132</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4141,26 +4140,24 @@
         <v>77</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>210</v>
+        <v>134</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="O27" t="s" s="2">
-        <v>142</v>
-      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
       </c>
@@ -4208,7 +4205,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4226,7 +4223,7 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>130</v>
+        <v>204</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4235,44 +4232,48 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>77</v>
+        <v>209</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>200</v>
+        <v>133</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>239</v>
+        <v>210</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
@@ -4320,39 +4321,39 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>175</v>
+        <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="29" hidden="true">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4375,7 +4376,7 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>244</v>
@@ -4432,7 +4433,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4450,34 +4451,128 @@
         <v>175</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="AM29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN29" t="s" s="2">
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
         <v>247</v>
       </c>
+      <c r="B30" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>252</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN29">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI28">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/fhir/finnish-smart/StructureDefinition-fi-smart-medication.xlsx
+++ b/fhir/finnish-smart/StructureDefinition-fi-smart-medication.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$29</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="248">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-rc3</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-01T15:36:45+03:00</t>
+    <t>2025-10-26T13:24:16+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://hl7.fi/fhir/finnish-base-profiles/StructureDefinition/fi-base-medication</t>
+    <t>http://hl7.org/fhir/uv/ipa/StructureDefinition/ipa-medication</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -558,7 +561,7 @@
     <t>Medication.manufacturer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fi/fhir/finnish-base-profiles/StructureDefinition/fi-base-organization)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -705,27 +708,10 @@
     <t>The ingredient may reference a substance (for example, amoxicillin) or another medication (for example in the case of a compounded product, Glaxal Base).</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>.player</t>
   </si>
   <si>
     <t>RXC-2-Component Code  if medication: RXO-1-Requested Give Code / RXE-2-Give Code / RXD-2-Dispense/Give Code / RXG-4-Give Code / RXA-5-Administered Code</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemReference</t>
-  </si>
-  <si>
-    <t>itemReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Substance|https://hl7.fi/fhir/finnish-base-profiles/StructureDefinition/fi-base-medication|https://hl7.fi/fhir/finnish-base-profiles/StructureDefinition/fi-base-patient-medication)
-</t>
   </si>
   <si>
     <t>Medication.ingredient.isActive</t>
@@ -941,6 +927,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1114,12 +1115,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN30"/>
+  <dimension ref="A1:AN29"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="34.99609375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="32.10546875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="32.10546875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="9.79296875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
@@ -1127,7 +1128,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="148.640625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="26.21875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1280,7 +1281,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -1392,7 +1393,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>86</v>
       </c>
@@ -1506,7 +1507,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>94</v>
       </c>
@@ -1618,7 +1619,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>100</v>
       </c>
@@ -1732,7 +1733,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>106</v>
       </c>
@@ -1846,7 +1847,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>115</v>
       </c>
@@ -1960,7 +1961,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>123</v>
       </c>
@@ -2074,7 +2075,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>131</v>
       </c>
@@ -2188,7 +2189,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>139</v>
       </c>
@@ -2304,7 +2305,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>144</v>
       </c>
@@ -2431,13 +2432,13 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>77</v>
@@ -2532,7 +2533,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>163</v>
       </c>
@@ -2646,7 +2647,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>171</v>
       </c>
@@ -2758,7 +2759,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>179</v>
       </c>
@@ -2872,7 +2873,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>188</v>
       </c>
@@ -2984,7 +2985,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>193</v>
       </c>
@@ -3098,7 +3099,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>199</v>
       </c>
@@ -3210,7 +3211,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>205</v>
       </c>
@@ -3324,7 +3325,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>208</v>
       </c>
@@ -3440,7 +3441,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>213</v>
       </c>
@@ -3515,14 +3516,16 @@
         <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AC21" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>219</v>
+        <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>213</v>
@@ -3543,25 +3546,23 @@
         <v>159</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="22" hidden="true">
+      <c r="A22" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AM21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>222</v>
-      </c>
       <c r="B22" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>77</v>
       </c>
@@ -3582,17 +3583,17 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -3641,10 +3642,10 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>87</v>
@@ -3656,24 +3657,24 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3696,7 +3697,7 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>227</v>
@@ -3705,9 +3706,7 @@
         <v>228</v>
       </c>
       <c r="N23" s="2"/>
-      <c r="O23" t="s" s="2">
-        <v>229</v>
-      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>77</v>
       </c>
@@ -3755,7 +3754,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3770,19 +3769,19 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>77</v>
+        <v>229</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AM23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="24">
+    </row>
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>231</v>
       </c>
@@ -3810,7 +3809,7 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>232</v>
@@ -3882,24 +3881,24 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="AL24" t="s" s="2">
-        <v>192</v>
-      </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN24" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" hidden="true">
+      <c r="A25" t="s" s="2">
         <v>235</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="2">
-        <v>236</v>
-      </c>
       <c r="B25" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3922,13 +3921,13 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3979,7 +3978,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>236</v>
+        <v>203</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -3991,13 +3990,13 @@
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>175</v>
+        <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>239</v>
+        <v>204</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4006,23 +4005,23 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4034,15 +4033,17 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>200</v>
+        <v>133</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>201</v>
+        <v>134</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4091,19 +4092,19 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
@@ -4118,16 +4119,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>132</v>
+        <v>209</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4140,24 +4141,26 @@
         <v>77</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>134</v>
+        <v>210</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="O27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
       </c>
@@ -4205,7 +4208,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4223,7 +4226,7 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4232,48 +4235,44 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>209</v>
+        <v>77</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>133</v>
+        <v>200</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
@@ -4321,39 +4320,39 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4376,7 +4375,7 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>200</v>
+        <v>243</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>244</v>
@@ -4433,7 +4432,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4451,128 +4450,34 @@
         <v>175</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>149</v>
+        <v>246</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="B30" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E30" s="2"/>
-      <c r="F30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G30" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K30" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
-      <c r="P30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q30" s="2"/>
-      <c r="R30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>252</v>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN29">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI28">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>